--- a/sheets/조재수대금교본/검수/가시리.xlsx
+++ b/sheets/조재수대금교본/검수/가시리.xlsx
@@ -2390,11 +2390,7 @@
       <c r="K9" s="23"/>
       <c r="L9" s="21"/>
       <c r="M9" s="23"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N9" s="21"/>
       <c r="O9" s="23"/>
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
@@ -2409,11 +2405,7 @@
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -2421,11 +2413,7 @@
         </is>
       </c>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -2451,11 +2439,7 @@
       <c r="O10" s="24"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/가시리.xlsx
+++ b/sheets/조재수대금교본/검수/가시리.xlsx
@@ -2040,30 +2040,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="144.08" customHeight="true">
+    <row r="3" ht="159.59" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="144.08" customHeight="true">
+    <row r="4" ht="159.59" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="144.08" customHeight="true">
+    <row r="5" ht="159.59" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="144.08" customHeight="true">
+    <row r="6" ht="159.59" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="144.08" customHeight="true">
+    <row r="7" ht="159.59" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="144.08" customHeight="true">
+    <row r="8" ht="159.59" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="144.08" customHeight="true">
+    <row r="9" ht="159.59" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2397,7 +2397,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="144.08" customHeight="true">
+    <row r="10" ht="159.59" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2448,6 +2448,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>